--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,6 +1913,1609 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128585687</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577616</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7021446</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128585699</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577600</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7021457</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128585701</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577601</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7021387</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128585691</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577518</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7021469</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128585679</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577544</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7021369</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128585677</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577549</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7021378</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128585696</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577618</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7021446</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128585675</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>577541</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7021357</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128585690</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>577550</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7021476</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128585697</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>577619</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7021447</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128585685</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>577597</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7021410</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128585700</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91452</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>577486</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7021397</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128585676</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>577546</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7021364</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128585680</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>577618</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7021402</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128585698</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>577613</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7021449</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128585678</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>577546</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7021384</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128585701</v>
+        <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>80188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,39 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577601</v>
+        <v>577518</v>
       </c>
       <c r="R15" t="n">
-        <v>7021387</v>
+        <v>7021469</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2183,12 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128585691</v>
+        <v>128585701</v>
       </c>
       <c r="B16" t="n">
-        <v>80188</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,34 +2221,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577518</v>
+        <v>577601</v>
       </c>
       <c r="R16" t="n">
-        <v>7021469</v>
+        <v>7021387</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>128585701</v>
       </c>
       <c r="B16" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>128585679</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>128585677</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>128585675</v>
       </c>
       <c r="B20" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91452</v>
+        <v>91458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>128585676</v>
       </c>
       <c r="B25" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128585680</v>
       </c>
       <c r="B26" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>128585678</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91458</v>
+        <v>91464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91464</v>
+        <v>91466</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128585691</v>
+        <v>128585701</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>57716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,34 +2124,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577518</v>
+        <v>577601</v>
       </c>
       <c r="R15" t="n">
-        <v>7021469</v>
+        <v>7021387</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2178,12 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128585701</v>
+        <v>128585691</v>
       </c>
       <c r="B16" t="n">
-        <v>57689</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,39 +2226,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577601</v>
+        <v>577518</v>
       </c>
       <c r="R16" t="n">
-        <v>7021387</v>
+        <v>7021469</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,7 +2315,7 @@
         <v>128585679</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>128585677</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>128585675</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>128585676</v>
       </c>
       <c r="B25" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128585680</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>128585678</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128585701</v>
+        <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>57716</v>
+        <v>80221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,39 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577601</v>
+        <v>577518</v>
       </c>
       <c r="R15" t="n">
-        <v>7021387</v>
+        <v>7021469</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2183,12 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128585691</v>
+        <v>128585701</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>57716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,34 +2221,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577518</v>
+        <v>577601</v>
       </c>
       <c r="R16" t="n">
-        <v>7021469</v>
+        <v>7021387</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>128585701</v>
       </c>
       <c r="B16" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>128585679</v>
       </c>
       <c r="B17" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>128585677</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>128585675</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>128585676</v>
       </c>
       <c r="B25" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>128585680</v>
       </c>
       <c r="B26" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>128585678</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128585691</v>
+        <v>128585701</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,34 +2124,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577518</v>
+        <v>577601</v>
       </c>
       <c r="R15" t="n">
-        <v>7021469</v>
+        <v>7021387</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2178,12 +2183,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2210,10 +2215,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128585701</v>
+        <v>128585691</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,39 +2226,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577601</v>
+        <v>577518</v>
       </c>
       <c r="R16" t="n">
-        <v>7021387</v>
+        <v>7021469</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3111,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128585676</v>
+        <v>128585680</v>
       </c>
       <c r="B25" t="n">
         <v>57720</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577546</v>
+        <v>577618</v>
       </c>
       <c r="R25" t="n">
-        <v>7021364</v>
+        <v>7021402</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128585680</v>
+        <v>128585676</v>
       </c>
       <c r="B26" t="n">
         <v>57720</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577618</v>
+        <v>577546</v>
       </c>
       <c r="R26" t="n">
-        <v>7021402</v>
+        <v>7021364</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128585701</v>
+        <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,39 +2124,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577601</v>
+        <v>577518</v>
       </c>
       <c r="R15" t="n">
-        <v>7021387</v>
+        <v>7021469</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2183,12 +2178,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2215,10 +2210,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128585691</v>
+        <v>128585701</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,34 +2221,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577518</v>
+        <v>577601</v>
       </c>
       <c r="R16" t="n">
-        <v>7021469</v>
+        <v>7021387</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,7 +2315,7 @@
         <v>128585679</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>128585677</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>128585675</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128585680</v>
+        <v>128585676</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577618</v>
+        <v>577546</v>
       </c>
       <c r="R25" t="n">
-        <v>7021402</v>
+        <v>7021364</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,10 +3213,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128585676</v>
+        <v>128585680</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577546</v>
+        <v>577618</v>
       </c>
       <c r="R26" t="n">
-        <v>7021364</v>
+        <v>7021402</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>128585678</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91515</v>
+        <v>91520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128585676</v>
+        <v>128585680</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577546</v>
+        <v>577618</v>
       </c>
       <c r="R25" t="n">
-        <v>7021364</v>
+        <v>7021402</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128585680</v>
+        <v>128585676</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577618</v>
+        <v>577546</v>
       </c>
       <c r="R26" t="n">
-        <v>7021402</v>
+        <v>7021364</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -3111,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128585680</v>
+        <v>128585676</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577618</v>
+        <v>577546</v>
       </c>
       <c r="R25" t="n">
-        <v>7021402</v>
+        <v>7021364</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128585676</v>
+        <v>128585680</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577546</v>
+        <v>577618</v>
       </c>
       <c r="R26" t="n">
-        <v>7021364</v>
+        <v>7021402</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>128585687</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128585699</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128585691</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128585696</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128585690</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>128585697</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>128585685</v>
       </c>
       <c r="B23" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>128585700</v>
       </c>
       <c r="B24" t="n">
-        <v>91520</v>
+        <v>91526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>128585698</v>
       </c>
       <c r="B27" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -3111,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128585676</v>
+        <v>128585680</v>
       </c>
       <c r="B25" t="n">
         <v>57723</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577546</v>
+        <v>577618</v>
       </c>
       <c r="R25" t="n">
-        <v>7021364</v>
+        <v>7021402</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128585680</v>
+        <v>128585676</v>
       </c>
       <c r="B26" t="n">
         <v>57723</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577618</v>
+        <v>577546</v>
       </c>
       <c r="R26" t="n">
-        <v>7021402</v>
+        <v>7021364</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60284004</v>
+        <v>110398553</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vilseskogen, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577554.6731902066</v>
+        <v>577454</v>
       </c>
       <c r="R2" t="n">
-        <v>7021463.436069616</v>
+        <v>7021406</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,67 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60284034</v>
+        <v>121386650</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577627.8828057742</v>
+        <v>577482</v>
       </c>
       <c r="R3" t="n">
-        <v>7021452.613201797</v>
+        <v>7021393</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60284009</v>
+        <v>72916276</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,36 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Vilseskogen, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577554.6731902066</v>
+        <v>577535</v>
       </c>
       <c r="R4" t="n">
-        <v>7021463.436069616</v>
+        <v>7021470</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -975,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Elin Götmark, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60284031</v>
+        <v>110398551</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1033,39 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vilseskogen, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577627.8828057742</v>
+        <v>577454</v>
       </c>
       <c r="R5" t="n">
-        <v>7021452.613201797</v>
+        <v>7021406</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-06-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>60342426</v>
+        <v>121386613</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,39 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577600.630950731</v>
+        <v>577479</v>
       </c>
       <c r="R6" t="n">
-        <v>7021462.297539178</v>
+        <v>7021437</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2016-06-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2016-06-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,65 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72916277</v>
+        <v>121386614</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gässjö, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577492.8935202959</v>
+        <v>577477</v>
       </c>
       <c r="R7" t="n">
-        <v>7021411.130307732</v>
+        <v>7021416</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Götmark, Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>72916276</v>
+        <v>121386615</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,17 +1288,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gässjö, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577535.159004283</v>
+        <v>577481</v>
       </c>
       <c r="R8" t="n">
-        <v>7021469.710263102</v>
+        <v>7021393</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Götmark, Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>72916275</v>
+        <v>121386616</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,37 +1365,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gässjö, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577535.159004283</v>
+        <v>577485</v>
       </c>
       <c r="R9" t="n">
-        <v>7021469.710263102</v>
+        <v>7021401</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,67 +1439,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Götmark, Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73175416</v>
+        <v>128585700</v>
       </c>
       <c r="B10" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vilseskogen, Ång</t>
+          <t>vilseskogen södra, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577604.6508719361</v>
+        <v>577486</v>
       </c>
       <c r="R10" t="n">
-        <v>7021389.095049921</v>
+        <v>7021397</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-09-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,49 +1530,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Eino Kenttä</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121386616</v>
+        <v>72916278</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vilseskogen, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577485</v>
+        <v>577471</v>
       </c>
       <c r="R11" t="n">
-        <v>7021401</v>
+        <v>7021411</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Elin Götmark, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121386671</v>
+        <v>72916275</v>
       </c>
       <c r="B12" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vilseskogen, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577486</v>
+        <v>577535</v>
       </c>
       <c r="R12" t="n">
-        <v>7021400</v>
+        <v>7021470</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1883,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1903,22 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Elin Götmark, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128585687</v>
+        <v>110398556</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,37 +1753,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577616</v>
+        <v>577454</v>
       </c>
       <c r="R13" t="n">
-        <v>7021446</v>
+        <v>7021406</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1980,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,64 +1827,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128585699</v>
+        <v>60284009</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577600</v>
+        <v>577555</v>
       </c>
       <c r="R14" t="n">
-        <v>7021457</v>
+        <v>7021463</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2081,12 +1906,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,22 +1926,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128585691</v>
+        <v>60326856</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,37 +1949,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577518</v>
+        <v>577644</v>
       </c>
       <c r="R15" t="n">
-        <v>7021469</v>
+        <v>7021457</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2178,12 +2005,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,69 +2021,81 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128585701</v>
+        <v>73175416</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577601</v>
+        <v>577605</v>
       </c>
       <c r="R16" t="n">
-        <v>7021387</v>
+        <v>7021389</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2280,12 +2119,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2018-09-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,71 +2133,82 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128585679</v>
+        <v>72916277</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577544</v>
+        <v>577493</v>
       </c>
       <c r="R17" t="n">
-        <v>7021369</v>
+        <v>7021411</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,12 +2232,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,65 +2252,60 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Elin Götmark, Eino Kenttä</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128585677</v>
+        <v>110398554</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577549</v>
+        <v>577454</v>
       </c>
       <c r="R18" t="n">
-        <v>7021378</v>
+        <v>7021406</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2484,12 +2329,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2504,22 +2349,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128585696</v>
+        <v>110398555</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,41 +2372,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577618</v>
+        <v>577454</v>
       </c>
       <c r="R19" t="n">
-        <v>7021446</v>
+        <v>7021406</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,12 +2426,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2605,65 +2446,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128585675</v>
+        <v>61915511</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>80336</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>577541</v>
+        <v>577521</v>
       </c>
       <c r="R20" t="n">
-        <v>7021357</v>
+        <v>7021500</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2687,12 +2525,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2703,26 +2541,46 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Relativt tunn men förmodligen gammal asp.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula # Relativt tunn men förmodligen gammal asp.</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128585690</v>
+        <v>60283988</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,19 +2606,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>577550</v>
+        <v>577486</v>
       </c>
       <c r="R21" t="n">
-        <v>7021476</v>
+        <v>7021395</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2784,12 +2644,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2804,64 +2664,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128585697</v>
+        <v>60284004</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>577619</v>
+        <v>577555</v>
       </c>
       <c r="R22" t="n">
-        <v>7021447</v>
+        <v>7021463</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2885,12 +2743,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2905,22 +2763,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128585685</v>
+        <v>60284017</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,19 +2804,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577597</v>
+        <v>577585</v>
       </c>
       <c r="R23" t="n">
-        <v>7021410</v>
+        <v>7021476</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,12 +2842,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3002,22 +2862,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128585700</v>
+        <v>60284031</v>
       </c>
       <c r="B24" t="n">
-        <v>91526</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,37 +2885,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577486</v>
+        <v>577628</v>
       </c>
       <c r="R24" t="n">
-        <v>7021397</v>
+        <v>7021453</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3079,12 +2941,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2016-06-25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3099,22 +2961,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128585680</v>
+        <v>60342426</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3122,42 +2984,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577618</v>
+        <v>577601</v>
       </c>
       <c r="R25" t="n">
-        <v>7021402</v>
+        <v>7021462</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3181,12 +3040,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-06-28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3201,22 +3060,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128585676</v>
+        <v>61310116</v>
       </c>
       <c r="B26" t="n">
-        <v>57723</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,42 +3083,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577546</v>
+        <v>577584</v>
       </c>
       <c r="R26" t="n">
-        <v>7021364</v>
+        <v>7021497</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3283,12 +3139,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-07-16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-07-16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3299,68 +3155,81 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128585698</v>
+        <v>61915515</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Vilseskogen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>577613</v>
+        <v>577521</v>
       </c>
       <c r="R27" t="n">
-        <v>7021449</v>
+        <v>7021500</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3384,12 +3253,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2016-10-24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3400,26 +3269,46 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>Relativt tunn men förmodligen gammal asp.</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Populus tremula # Relativt tunn men förmodligen gammal asp.</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Eino Kenttä</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128585678</v>
+        <v>110398569</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,42 +3316,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>vilseskogen södra, Ång</t>
+          <t>Gässjö, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>577546</v>
+        <v>577554</v>
       </c>
       <c r="R28" t="n">
-        <v>7021384</v>
+        <v>7021492</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3486,12 +3370,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3506,15 +3390,2605 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121386671</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vilseskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>577486</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7021400</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Dennis Pålsson</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Dennis Pålsson</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128585685</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>577597</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7021410</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128585686</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>577654</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7021370</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128585687</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>577616</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7021446</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128585688</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>577568</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7021481</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128585689</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>577554</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7021482</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128585690</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>577550</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7021476</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128585691</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>577518</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7021469</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128585702</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>577484</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7021396</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>60284034</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Vilseskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>577628</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7021453</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2016-06-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eino Kenttä</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eino Kenttä</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>110398567</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gässjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>577554</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7021492</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>110398568</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gässjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>577554</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7021492</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128585675</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>577541</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7021357</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128585676</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>577546</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7021364</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128585677</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>577549</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7021378</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128585678</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>577546</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7021384</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128585679</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>577544</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7021369</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128585680</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>577618</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7021402</v>
+      </c>
+      <c r="S46" t="n">
+        <v>20</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128585681</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>577660</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7021372</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128585701</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>577601</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7021387</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>61310137</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Vilseskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>577584</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7021497</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eino Kenttä</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eino Kenttä</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128585696</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>577618</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7021446</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128585697</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>577619</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7021447</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128585698</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>577613</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7021449</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128585699</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>vilseskogen södra, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>577600</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7021457</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>61310105</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Vilseskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>577584</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7021497</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2016-07-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Eino Kenttä</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Eino Kenttä</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39197-2025 artfynd.xlsx
+++ b/artfynd/A 39197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398553</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121386650</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72916276</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121386613</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121386614</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121386615</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121386616</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585700</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72916278</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72916275</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398556</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1935,6 +2000,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60284009</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2049,6 +2119,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60326856</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2164,6 +2239,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73175416</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2261,6 +2341,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72916277</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2358,6 +2443,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398554</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2455,6 +2545,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398555</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2574,6 +2669,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61915511</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2673,6 +2773,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60283988</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2772,6 +2877,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60284004</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2871,6 +2981,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60284017</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2970,6 +3085,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60284031</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3069,6 +3189,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60342426</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3183,6 +3308,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61310116</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,6 +3432,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61915515</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3399,6 +3534,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398569</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3496,6 +3636,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121386671</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3593,6 +3738,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585685</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3690,6 +3840,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585686</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3787,6 +3942,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585687</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3884,6 +4044,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585688</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3981,6 +4146,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585689</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4078,6 +4248,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585690</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4175,6 +4350,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585691</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4272,6 +4452,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585702</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4371,6 +4556,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60284034</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4468,6 +4658,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398567</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4565,6 +4760,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110398568</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4667,6 +4867,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585675</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4769,6 +4974,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585676</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4871,6 +5081,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585677</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4973,6 +5188,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585678</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5075,6 +5295,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585679</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5177,6 +5402,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585680</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5279,6 +5509,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585681</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5381,6 +5616,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585701</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5485,6 +5725,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61310137</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5586,6 +5831,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585696</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5687,6 +5937,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585697</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5788,6 +6043,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585698</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5889,6 +6149,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128585699</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5989,8 +6254,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61310105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>